--- a/Decks/Pests.xlsx
+++ b/Decks/Pests.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6BAFC19-B97A-411C-AA4B-B891494A244B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E67C5BA-972C-4689-9B7B-17E25E235C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7CE25059-BB48-4452-96A8-6E88175C1C7D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="128">
   <si>
     <t>Função</t>
   </si>
@@ -332,9 +332,6 @@
     <t>Trespasser's Curse</t>
   </si>
   <si>
-    <t>Origin of Metalbending</t>
-  </si>
-  <si>
     <t>Vraska's Contempt</t>
   </si>
   <si>
@@ -399,12 +396,6 @@
   </si>
   <si>
     <t>Wolfbat</t>
-  </si>
-  <si>
-    <t>Scute Mob</t>
-  </si>
-  <si>
-    <t>Blightbeetle</t>
   </si>
   <si>
     <t>Gala Greeters</t>
@@ -1325,7 +1316,7 @@
         <v>1</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>73</v>
@@ -1340,7 +1331,7 @@
         <v>1</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>70</v>
@@ -1385,10 +1376,10 @@
         <v>0</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1400,7 +1391,7 @@
         <v>1</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>58</v>
@@ -1430,7 +1421,7 @@
         <v>1</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>54</v>
@@ -1460,7 +1451,7 @@
         <v>1</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>50</v>
@@ -1475,10 +1466,10 @@
         <v>0</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1505,10 +1496,10 @@
         <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1550,7 +1541,7 @@
         <v>1</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>29</v>
@@ -1565,7 +1556,7 @@
         <v>1</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>39</v>
@@ -1580,7 +1571,7 @@
         <v>1</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>46</v>
@@ -1715,7 +1706,7 @@
         <v>1</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>34</v>
@@ -1730,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>66</v>
@@ -1745,10 +1736,10 @@
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -1775,7 +1766,7 @@
         <v>1</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>31</v>
@@ -1805,7 +1796,7 @@
         <v>1</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>14</v>
@@ -1820,7 +1811,7 @@
         <v>1</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>64</v>
@@ -1835,7 +1826,7 @@
         <v>1</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>65</v>
@@ -1850,7 +1841,7 @@
         <v>1</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>28</v>
@@ -1865,7 +1856,7 @@
         <v>1</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>51</v>
@@ -1895,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>86</v>
@@ -1952,10 +1943,10 @@
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>122</v>
+        <v>37</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>37</v>
@@ -2015,7 +2006,7 @@
         <v>1</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>24</v>
@@ -2030,7 +2021,7 @@
         <v>1</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>25</v>
@@ -2045,7 +2036,7 @@
         <v>1</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>26</v>
@@ -2057,10 +2048,10 @@
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>27</v>
@@ -2072,10 +2063,10 @@
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>121</v>
+        <v>32</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>32</v>
@@ -2090,7 +2081,7 @@
         <v>1</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>35</v>
@@ -2105,7 +2096,7 @@
         <v>1</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>36</v>
@@ -2120,7 +2111,7 @@
         <v>1</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>40</v>
@@ -2180,7 +2171,7 @@
         <v>1</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>48</v>
@@ -2210,7 +2201,7 @@
         <v>1</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>33</v>
@@ -2240,7 +2231,7 @@
         <v>1</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>12</v>

--- a/Decks/Pests.xlsx
+++ b/Decks/Pests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E67C5BA-972C-4689-9B7B-17E25E235C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90694935-947B-4996-B715-6756B89BA777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7CE25059-BB48-4452-96A8-6E88175C1C7D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="123">
   <si>
     <t>Função</t>
   </si>
@@ -125,9 +125,6 @@
     <t>Blex, Vexing Pest</t>
   </si>
   <si>
-    <t>Essence Warden</t>
-  </si>
-  <si>
     <t>Duskshell Crawler</t>
   </si>
   <si>
@@ -155,9 +152,6 @@
     <t>Bolas's Citadel</t>
   </si>
   <si>
-    <t>Virulent Emissary</t>
-  </si>
-  <si>
     <t>Pest Rescuer</t>
   </si>
   <si>
@@ -212,9 +206,6 @@
     <t>Putrefy</t>
   </si>
   <si>
-    <t>Return of the Wildspeaker</t>
-  </si>
-  <si>
     <t>Pest Summoning</t>
   </si>
   <si>
@@ -254,12 +245,6 @@
     <t>Sanguine Bond</t>
   </si>
   <si>
-    <t>Lifegift</t>
-  </si>
-  <si>
-    <t>Terrasymbiosis</t>
-  </si>
-  <si>
     <t>Swarmyard</t>
   </si>
   <si>
@@ -353,9 +338,6 @@
     <t>Eventide's Shadow</t>
   </si>
   <si>
-    <t>Clackbridge Troll</t>
-  </si>
-  <si>
     <t>Stocking the Pantry</t>
   </si>
   <si>
@@ -420,6 +402,9 @@
   </si>
   <si>
     <t>Well of Lost Dreams</t>
+  </si>
+  <si>
+    <t>Mask of Griselbrand</t>
   </si>
 </sst>
 </file>
@@ -877,10 +862,10 @@
         <v>0</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -906,7 +891,7 @@
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -919,7 +904,7 @@
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -932,7 +917,7 @@
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -945,7 +930,7 @@
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -972,10 +957,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -988,7 +973,7 @@
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1000,10 +985,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1016,7 +1001,7 @@
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1029,7 +1014,7 @@
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1042,7 +1027,7 @@
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1054,10 +1039,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1070,7 +1055,7 @@
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1083,7 +1068,7 @@
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1096,7 +1081,7 @@
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1109,7 +1094,7 @@
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1122,7 +1107,7 @@
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1135,7 +1120,7 @@
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1148,7 +1133,7 @@
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1161,7 +1146,7 @@
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1174,7 +1159,7 @@
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1187,7 +1172,7 @@
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1200,7 +1185,7 @@
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1213,7 +1198,7 @@
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1226,7 +1211,7 @@
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1239,7 +1224,7 @@
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1252,7 +1237,7 @@
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1265,7 +1250,7 @@
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1278,7 +1263,7 @@
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1291,7 +1276,7 @@
       </c>
       <c r="C35" s="4"/>
       <c r="D35" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1304,7 +1289,7 @@
       </c>
       <c r="C36" s="4"/>
       <c r="D36" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1313,13 +1298,13 @@
       </c>
       <c r="B37" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>73</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1331,10 +1316,10 @@
         <v>1</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1346,10 +1331,10 @@
         <v>0</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1361,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1376,10 +1361,10 @@
         <v>0</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1388,13 +1373,13 @@
       </c>
       <c r="B42" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>58</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1406,10 +1391,10 @@
         <v>0</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1421,10 +1406,10 @@
         <v>1</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1436,10 +1421,10 @@
         <v>0</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1451,10 +1436,10 @@
         <v>1</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1466,10 +1451,10 @@
         <v>0</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1481,10 +1466,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1496,10 +1481,10 @@
         <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1538,13 +1523,13 @@
       </c>
       <c r="B52" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>29</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1553,13 +1538,13 @@
       </c>
       <c r="B53" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>39</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1571,10 +1556,10 @@
         <v>1</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -1586,10 +1571,10 @@
         <v>1</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -1601,10 +1586,10 @@
         <v>0</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -1613,13 +1598,13 @@
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -1631,70 +1616,70 @@
         <v>1</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B59" s="5" t="b">
         <f>C59&lt;&gt;D59</f>
         <v>1</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B60" s="5" t="b">
         <f>C60&lt;&gt;D60</f>
         <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B62" s="5" t="b">
         <f>C62&lt;&gt;D62</f>
         <v>1</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -1706,10 +1691,10 @@
         <v>1</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -1721,10 +1706,10 @@
         <v>1</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -1736,10 +1721,10 @@
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -1751,10 +1736,10 @@
         <v>0</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -1766,10 +1751,10 @@
         <v>1</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -1781,10 +1766,10 @@
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -1796,7 +1781,7 @@
         <v>1</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>14</v>
@@ -1811,10 +1796,10 @@
         <v>1</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -1826,10 +1811,10 @@
         <v>1</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -1841,7 +1826,7 @@
         <v>1</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>28</v>
@@ -1856,10 +1841,10 @@
         <v>1</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -1871,10 +1856,10 @@
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -1886,10 +1871,10 @@
         <v>1</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -1901,10 +1886,10 @@
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -1916,10 +1901,10 @@
         <v>0</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -1931,10 +1916,10 @@
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -1946,10 +1931,10 @@
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -1961,10 +1946,10 @@
         <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -1976,10 +1961,10 @@
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -2006,7 +1991,7 @@
         <v>1</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>24</v>
@@ -2021,7 +2006,7 @@
         <v>1</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>25</v>
@@ -2036,7 +2021,7 @@
         <v>1</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>26</v>
@@ -2066,10 +2051,10 @@
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -2081,10 +2066,10 @@
         <v>1</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -2096,10 +2081,10 @@
         <v>1</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -2111,10 +2096,10 @@
         <v>1</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -2126,10 +2111,10 @@
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -2141,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -2156,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -2171,10 +2156,10 @@
         <v>1</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -2201,10 +2186,10 @@
         <v>1</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -2216,10 +2201,10 @@
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -2231,7 +2216,7 @@
         <v>1</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>12</v>
@@ -2261,10 +2246,10 @@
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -2276,10 +2261,10 @@
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Pests.xlsx
+++ b/Decks/Pests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90694935-947B-4996-B715-6756B89BA777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D42B12D7-3FBE-41F0-8D55-ECCB26640818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7CE25059-BB48-4452-96A8-6E88175C1C7D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="122">
   <si>
     <t>Função</t>
   </si>
@@ -194,9 +194,6 @@
     <t>Pestbrood Sloth</t>
   </si>
   <si>
-    <t>Scheming Silvertongue</t>
-  </si>
-  <si>
     <t>Basilica Screecher</t>
   </si>
   <si>
@@ -341,9 +338,6 @@
     <t>Stocking the Pantry</t>
   </si>
   <si>
-    <t>Deathreap Ritual</t>
-  </si>
-  <si>
     <t>Road of Return</t>
   </si>
   <si>
@@ -405,6 +399,9 @@
   </si>
   <si>
     <t>Mask of Griselbrand</t>
+  </si>
+  <si>
+    <t>Scheming Silvertong // Sign in Blood</t>
   </si>
 </sst>
 </file>
@@ -862,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -891,7 +888,7 @@
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -904,7 +901,7 @@
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -917,7 +914,7 @@
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -930,7 +927,7 @@
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -957,10 +954,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -973,7 +970,7 @@
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -985,10 +982,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1001,7 +998,7 @@
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1014,7 +1011,7 @@
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1027,7 +1024,7 @@
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1039,10 +1036,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1055,7 +1052,7 @@
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1068,7 +1065,7 @@
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1081,7 +1078,7 @@
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1094,7 +1091,7 @@
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1107,7 +1104,7 @@
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1120,7 +1117,7 @@
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1133,7 +1130,7 @@
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1146,7 +1143,7 @@
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1159,7 +1156,7 @@
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1172,7 +1169,7 @@
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1185,7 +1182,7 @@
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1198,7 +1195,7 @@
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1211,7 +1208,7 @@
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1224,7 +1221,7 @@
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1237,7 +1234,7 @@
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1250,7 +1247,7 @@
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1263,7 +1260,7 @@
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1276,7 +1273,7 @@
       </c>
       <c r="C35" s="4"/>
       <c r="D35" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1289,7 +1286,7 @@
       </c>
       <c r="C36" s="4"/>
       <c r="D36" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1301,10 +1298,10 @@
         <v>0</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1316,10 +1313,10 @@
         <v>1</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1331,10 +1328,10 @@
         <v>0</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1346,10 +1343,10 @@
         <v>0</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1361,10 +1358,10 @@
         <v>0</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1376,10 +1373,10 @@
         <v>0</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1391,10 +1388,10 @@
         <v>0</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1403,13 +1400,13 @@
       </c>
       <c r="B44" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>52</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1436,7 +1433,7 @@
         <v>1</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>48</v>
@@ -1451,10 +1448,10 @@
         <v>0</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1481,10 +1478,10 @@
         <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1526,10 +1523,10 @@
         <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1541,10 +1538,10 @@
         <v>0</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1556,7 +1553,7 @@
         <v>1</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>44</v>
@@ -1571,10 +1568,10 @@
         <v>1</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -1586,10 +1583,10 @@
         <v>0</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -1601,10 +1598,10 @@
         <v>0</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -1616,7 +1613,7 @@
         <v>1</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>47</v>
@@ -1624,14 +1621,14 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B59" s="5" t="b">
         <f>C59&lt;&gt;D59</f>
         <v>1</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>40</v>
@@ -1639,22 +1636,22 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B60" s="5" t="b">
         <f>C60&lt;&gt;D60</f>
         <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1669,14 +1666,14 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B62" s="5" t="b">
         <f>C62&lt;&gt;D62</f>
         <v>1</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>39</v>
@@ -1691,7 +1688,7 @@
         <v>1</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>33</v>
@@ -1706,10 +1703,10 @@
         <v>1</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -1721,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -1751,7 +1748,7 @@
         <v>1</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>30</v>
@@ -1766,10 +1763,10 @@
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -1781,7 +1778,7 @@
         <v>1</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>14</v>
@@ -1796,10 +1793,10 @@
         <v>1</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -1811,10 +1808,10 @@
         <v>1</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -1826,7 +1823,7 @@
         <v>1</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>28</v>
@@ -1841,7 +1838,7 @@
         <v>1</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>49</v>
@@ -1871,10 +1868,10 @@
         <v>1</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -1886,10 +1883,10 @@
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -1901,10 +1898,10 @@
         <v>0</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -1916,10 +1913,10 @@
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -1946,10 +1943,10 @@
         <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -1961,10 +1958,10 @@
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -1991,7 +1988,7 @@
         <v>1</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>24</v>
@@ -2006,7 +2003,7 @@
         <v>1</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>25</v>
@@ -2021,7 +2018,7 @@
         <v>1</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>26</v>
@@ -2066,7 +2063,7 @@
         <v>1</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>34</v>
@@ -2081,7 +2078,7 @@
         <v>1</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>35</v>
@@ -2096,7 +2093,7 @@
         <v>1</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>38</v>
@@ -2156,7 +2153,7 @@
         <v>1</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>46</v>
@@ -2186,7 +2183,7 @@
         <v>1</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>32</v>
@@ -2201,10 +2198,10 @@
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -2216,7 +2213,7 @@
         <v>1</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>12</v>
@@ -2246,10 +2243,10 @@
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -2261,10 +2258,10 @@
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Pests.xlsx
+++ b/Decks/Pests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D42B12D7-3FBE-41F0-8D55-ECCB26640818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A13B68B-E3C5-4C85-9F73-50E45D56C7BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7CE25059-BB48-4452-96A8-6E88175C1C7D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="121">
   <si>
     <t>Função</t>
   </si>
@@ -327,9 +327,6 @@
   </si>
   <si>
     <t>Erebos, Bleak-Hearted</t>
-  </si>
-  <si>
-    <t>Greed</t>
   </si>
   <si>
     <t>Eventide's Shadow</t>
@@ -1298,10 +1295,10 @@
         <v>0</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1310,10 +1307,10 @@
       </c>
       <c r="B38" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>66</v>
@@ -1373,10 +1370,10 @@
         <v>0</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1403,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1433,7 +1430,7 @@
         <v>1</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>48</v>
@@ -1523,10 +1520,10 @@
         <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1538,10 +1535,10 @@
         <v>0</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1553,7 +1550,7 @@
         <v>1</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>44</v>
@@ -1688,7 +1685,7 @@
         <v>1</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>33</v>
@@ -1703,7 +1700,7 @@
         <v>1</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>62</v>
@@ -1718,10 +1715,10 @@
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -1748,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>30</v>
@@ -1778,7 +1775,7 @@
         <v>1</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>14</v>
@@ -1793,7 +1790,7 @@
         <v>1</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>60</v>
@@ -1808,7 +1805,7 @@
         <v>1</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>61</v>
@@ -1823,7 +1820,7 @@
         <v>1</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>28</v>
@@ -1838,7 +1835,7 @@
         <v>1</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>49</v>
@@ -1868,7 +1865,7 @@
         <v>1</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>80</v>
@@ -1988,7 +1985,7 @@
         <v>1</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>24</v>
@@ -2003,7 +2000,7 @@
         <v>1</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>25</v>
@@ -2018,7 +2015,7 @@
         <v>1</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>26</v>
@@ -2063,7 +2060,7 @@
         <v>1</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>34</v>
@@ -2078,7 +2075,7 @@
         <v>1</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>35</v>
@@ -2093,7 +2090,7 @@
         <v>1</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>38</v>
@@ -2153,7 +2150,7 @@
         <v>1</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>46</v>

--- a/Decks/Pests.xlsx
+++ b/Decks/Pests.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A13B68B-E3C5-4C85-9F73-50E45D56C7BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D069033-296D-40A4-88A4-EAEB7C4BCF88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7CE25059-BB48-4452-96A8-6E88175C1C7D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="112">
   <si>
     <t>Função</t>
   </si>
@@ -74,9 +74,6 @@
     <t>Controle</t>
   </si>
   <si>
-    <t>Assassin's Trophy</t>
-  </si>
-  <si>
     <t>Mortality Spear</t>
   </si>
   <si>
@@ -110,9 +107,6 @@
     <t>Pest Mascot</t>
   </si>
   <si>
-    <t>Eccentric Pestfinder</t>
-  </si>
-  <si>
     <t>Tend the Pests</t>
   </si>
   <si>
@@ -134,9 +128,6 @@
     <t>Feral Appetite</t>
   </si>
   <si>
-    <t>Haywire Mite</t>
-  </si>
-  <si>
     <t>Twitching Doll</t>
   </si>
   <si>
@@ -152,9 +143,6 @@
     <t>Bolas's Citadel</t>
   </si>
   <si>
-    <t>Pest Rescuer</t>
-  </si>
-  <si>
     <t>Starscape Cleric</t>
   </si>
   <si>
@@ -182,9 +170,6 @@
     <t>Blood Artist</t>
   </si>
   <si>
-    <t>Dina, Essence Brewer</t>
-  </si>
-  <si>
     <t>Sedgemoor Witch</t>
   </si>
   <si>
@@ -239,9 +224,6 @@
     <t>Hollowmurk Siege</t>
   </si>
   <si>
-    <t>Sanguine Bond</t>
-  </si>
-  <si>
     <t>Swarmyard</t>
   </si>
   <si>
@@ -299,21 +281,12 @@
     <t>Terramorphic Expanse</t>
   </si>
   <si>
-    <t>Triskaidekaphobia</t>
-  </si>
-  <si>
     <t>Marauding Blight-Priest</t>
   </si>
   <si>
     <t>Earth Kingdom General</t>
   </si>
   <si>
-    <t>Basilisk Collar</t>
-  </si>
-  <si>
-    <t>Trespasser's Curse</t>
-  </si>
-  <si>
     <t>Vraska's Contempt</t>
   </si>
   <si>
@@ -332,33 +305,15 @@
     <t>Eventide's Shadow</t>
   </si>
   <si>
-    <t>Stocking the Pantry</t>
-  </si>
-  <si>
-    <t>Road of Return</t>
-  </si>
-  <si>
     <t>True Ancestry</t>
   </si>
   <si>
     <t>Winding Constrictor</t>
   </si>
   <si>
-    <t>Infuse with Vitality</t>
-  </si>
-  <si>
     <t>Beifong's Bounty Hunters</t>
   </si>
   <si>
-    <t>Primal Rage</t>
-  </si>
-  <si>
-    <t>Fortifying Draught</t>
-  </si>
-  <si>
-    <t>Garruk, Caller of Beasts</t>
-  </si>
-  <si>
     <t>Professor of Zoomancy</t>
   </si>
   <si>
@@ -374,18 +329,9 @@
     <t>Gala Greeters</t>
   </si>
   <si>
-    <t>Profane Memento</t>
-  </si>
-  <si>
     <t>Tablet of the Guilds</t>
   </si>
   <si>
-    <t>Jaddi Offshoot</t>
-  </si>
-  <si>
-    <t>Aetherflux Reservoir</t>
-  </si>
-  <si>
     <t>Temur Sabertooth</t>
   </si>
   <si>
@@ -399,6 +345,33 @@
   </si>
   <si>
     <t>Scheming Silvertong // Sign in Blood</t>
+  </si>
+  <si>
+    <t>Origin of Metalbending</t>
+  </si>
+  <si>
+    <t>Greed</t>
+  </si>
+  <si>
+    <t>Stock the Pantry</t>
+  </si>
+  <si>
+    <t>Deathreap Ritual</t>
+  </si>
+  <si>
+    <t>Reaper's Talisman</t>
+  </si>
+  <si>
+    <t>Unnatural Restoration</t>
+  </si>
+  <si>
+    <t>End-Raze Forerunners</t>
+  </si>
+  <si>
+    <t>Blightbeetle</t>
+  </si>
+  <si>
+    <t>Eccentric Pestfinder // Turn Stones</t>
   </si>
 </sst>
 </file>
@@ -828,10 +801,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -842,9 +815,11 @@
         <f t="shared" ref="B3:B55" si="0">C3&lt;&gt;D3</f>
         <v>1</v>
       </c>
-      <c r="C3" s="4"/>
+      <c r="C3" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="D3" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -856,10 +831,10 @@
         <v>0</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -870,9 +845,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="C5" s="4"/>
+      <c r="C5" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="D5" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -881,11 +858,13 @@
       </c>
       <c r="B6" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C6" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="D6" s="4" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -896,9 +875,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="C7" s="4"/>
+      <c r="C7" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="D7" s="4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -909,9 +890,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="C8" s="4"/>
+      <c r="C8" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="D8" s="4" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -922,9 +905,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="C9" s="4"/>
+      <c r="C9" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="D9" s="4" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -951,10 +936,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -965,9 +950,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="C12" s="4"/>
+      <c r="C12" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="D12" s="4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -976,13 +963,13 @@
       </c>
       <c r="B13" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>78</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -991,11 +978,13 @@
       </c>
       <c r="B14" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C14" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="D14" s="4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1006,9 +995,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="D15" s="4" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1019,9 +1010,11 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="C16" s="4"/>
+      <c r="C16" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="D16" s="4" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1033,10 +1026,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1045,11 +1038,13 @@
       </c>
       <c r="B18" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C18" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="D18" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1058,11 +1053,13 @@
       </c>
       <c r="B19" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C19" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="D19" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1071,11 +1068,13 @@
       </c>
       <c r="B20" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C20" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="D20" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1084,11 +1083,13 @@
       </c>
       <c r="B21" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C21" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="D21" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1097,11 +1098,13 @@
       </c>
       <c r="B22" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C22" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="D22" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1110,11 +1113,13 @@
       </c>
       <c r="B23" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C23" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="D23" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1123,11 +1128,13 @@
       </c>
       <c r="B24" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C24" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="D24" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1136,11 +1143,13 @@
       </c>
       <c r="B25" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C25" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="D25" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1149,11 +1158,13 @@
       </c>
       <c r="B26" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C26" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="D26" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1162,11 +1173,13 @@
       </c>
       <c r="B27" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C27" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="D27" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1175,11 +1188,13 @@
       </c>
       <c r="B28" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C28" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>77</v>
+      </c>
       <c r="D28" s="4" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1188,11 +1203,13 @@
       </c>
       <c r="B29" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C29" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="D29" s="4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1201,11 +1218,13 @@
       </c>
       <c r="B30" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C30" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="D30" s="4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1214,11 +1233,13 @@
       </c>
       <c r="B31" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C31" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="D31" s="4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1227,11 +1248,13 @@
       </c>
       <c r="B32" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C32" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="D32" s="4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1240,11 +1263,13 @@
       </c>
       <c r="B33" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C33" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="D33" s="4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1253,11 +1278,13 @@
       </c>
       <c r="B34" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C34" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="D34" s="4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1266,11 +1293,13 @@
       </c>
       <c r="B35" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C35" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="D35" s="4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1279,11 +1308,13 @@
       </c>
       <c r="B36" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C36" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>78</v>
+      </c>
       <c r="D36" s="4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1295,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1310,10 +1341,10 @@
         <v>0</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1325,10 +1356,10 @@
         <v>0</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1340,10 +1371,10 @@
         <v>0</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1355,10 +1386,10 @@
         <v>0</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1370,10 +1401,10 @@
         <v>0</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1385,10 +1416,10 @@
         <v>0</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1400,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1415,10 +1446,10 @@
         <v>0</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1427,13 +1458,13 @@
       </c>
       <c r="B46" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1445,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1460,10 +1491,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1475,205 +1506,205 @@
         <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B50" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B51" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B52" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B53" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B54" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>112</v>
+        <v>40</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B56" s="5" t="b">
         <f t="shared" ref="B56:B101" si="1">C56&lt;&gt;D56</f>
         <v>0</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B59" s="5" t="b">
         <f>C59&lt;&gt;D59</f>
         <v>1</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B60" s="5" t="b">
         <f>C60&lt;&gt;D60</f>
         <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B62" s="5" t="b">
         <f>C62&lt;&gt;D62</f>
         <v>1</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -1685,10 +1716,10 @@
         <v>1</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -1697,13 +1728,13 @@
       </c>
       <c r="B64" s="5" t="b">
         <f>C64&lt;&gt;D64</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -1715,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -1730,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -1745,10 +1776,10 @@
         <v>1</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -1760,10 +1791,10 @@
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -1775,10 +1806,10 @@
         <v>1</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -1790,10 +1821,10 @@
         <v>1</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -1805,355 +1836,355 @@
         <v>1</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B76" s="5" t="b">
         <f>C76&lt;&gt;D76</f>
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B78" s="5" t="b">
         <f>C78&lt;&gt;D78</f>
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>116</v>
+        <v>23</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>113</v>
+        <v>24</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -2165,10 +2196,10 @@
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -2177,13 +2208,13 @@
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -2195,10 +2226,10 @@
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -2207,13 +2238,13 @@
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -2225,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -2240,10 +2271,10 @@
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -2255,10 +2286,10 @@
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Pests.xlsx
+++ b/Decks/Pests.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D069033-296D-40A4-88A4-EAEB7C4BCF88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9B92EE-C6BE-413D-9565-AAFEC5BB99A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7CE25059-BB48-4452-96A8-6E88175C1C7D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="111">
   <si>
     <t>Função</t>
   </si>
@@ -320,21 +320,12 @@
     <t>The Hunger Tide Rises</t>
   </si>
   <si>
-    <t>Hornet Nest</t>
-  </si>
-  <si>
     <t>Wolfbat</t>
   </si>
   <si>
     <t>Gala Greeters</t>
   </si>
   <si>
-    <t>Tablet of the Guilds</t>
-  </si>
-  <si>
-    <t>Temur Sabertooth</t>
-  </si>
-  <si>
     <t>Cosmos Elixir</t>
   </si>
   <si>
@@ -344,18 +335,12 @@
     <t>Mask of Griselbrand</t>
   </si>
   <si>
-    <t>Scheming Silvertong // Sign in Blood</t>
-  </si>
-  <si>
     <t>Origin of Metalbending</t>
   </si>
   <si>
     <t>Greed</t>
   </si>
   <si>
-    <t>Stock the Pantry</t>
-  </si>
-  <si>
     <t>Deathreap Ritual</t>
   </si>
   <si>
@@ -372,6 +357,18 @@
   </si>
   <si>
     <t>Eccentric Pestfinder // Turn Stones</t>
+  </si>
+  <si>
+    <t>Path of Ancestry</t>
+  </si>
+  <si>
+    <t>Subterranean Cavern</t>
+  </si>
+  <si>
+    <t>Stocking the Pantry</t>
+  </si>
+  <si>
+    <t>Scheming Silvertongue // Sign in Blood</t>
   </si>
 </sst>
 </file>
@@ -873,10 +870,10 @@
       </c>
       <c r="B7" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>64</v>
@@ -948,10 +945,10 @@
       </c>
       <c r="B12" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>67</v>
@@ -963,10 +960,10 @@
       </c>
       <c r="B13" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>72</v>
@@ -1041,10 +1038,10 @@
         <v>0</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1056,10 +1053,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1326,10 +1323,10 @@
         <v>0</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1401,10 +1398,10 @@
         <v>0</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1431,10 +1428,10 @@
         <v>0</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1461,10 +1458,10 @@
         <v>0</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1551,10 +1548,10 @@
         <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1566,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1596,7 +1593,7 @@
         <v>1</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>47</v>
@@ -1656,7 +1653,7 @@
         <v>1</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>36</v>
@@ -1701,7 +1698,7 @@
         <v>1</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>35</v>
@@ -1713,10 +1710,10 @@
       </c>
       <c r="B63" s="5" t="b">
         <f>C63&lt;&gt;D63</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>30</v>
@@ -1806,7 +1803,7 @@
         <v>1</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>13</v>
@@ -1836,7 +1833,7 @@
         <v>1</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>56</v>
@@ -1851,7 +1848,7 @@
         <v>1</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>26</v>
@@ -1866,7 +1863,7 @@
         <v>1</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>44</v>
@@ -1893,10 +1890,10 @@
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>74</v>
@@ -2016,10 +2013,10 @@
         <v>1</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -2091,7 +2088,7 @@
         <v>1</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>31</v>
@@ -2103,10 +2100,10 @@
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>32</v>

--- a/Decks/Pests.xlsx
+++ b/Decks/Pests.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9B92EE-C6BE-413D-9565-AAFEC5BB99A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33F7AAB-F7F3-4AEB-B101-8A365C8B7BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7CE25059-BB48-4452-96A8-6E88175C1C7D}"/>
   </bookViews>
@@ -990,10 +990,10 @@
       </c>
       <c r="B15" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>69</v>
@@ -1005,10 +1005,10 @@
       </c>
       <c r="B16" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>70</v>
